--- a/実装したいもの.xlsx
+++ b/実装したいもの.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5126940-AA9A-4FFC-BC86-D68921D6C319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="3360" yWindow="2400" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,12 +15,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>実装したいもの</t>
     <rPh sb="0" eb="2">
@@ -150,23 +154,6 @@
     <t>スクエニ講評会のフィードバック</t>
     <rPh sb="4" eb="7">
       <t>コウヒョウカイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>カメラに当たり判定をつける</t>
-    <rPh sb="4" eb="5">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>カメラ制御なんとかしたい</t>
-    <rPh sb="3" eb="5">
-      <t>セイギョ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -174,7 +161,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -504,7 +491,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -513,7 +500,7 @@
     <col min="4" max="4" width="41.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -557,12 +544,8 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>14</v>
-      </c>
+      <c r="B7" s="1"/>
+      <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B8" s="1" t="s">
